--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4190"/>
+  <dimension ref="A1:F4191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84218,13 +84218,33 @@
         <v>69.98</v>
       </c>
       <c r="D4190" t="n">
-        <v>69.78</v>
+        <v>69.75</v>
       </c>
       <c r="E4190" t="n">
-        <v>69.98</v>
+        <v>69.83</v>
       </c>
       <c r="F4190" t="n">
-        <v>246</v>
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="4191">
+      <c r="A4191" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B4191" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="C4191" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="D4191" t="n">
+        <v>76.15000000000001</v>
+      </c>
+      <c r="E4191" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F4191" t="n">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4191"/>
+  <dimension ref="A1:F4192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84181,7 +84181,7 @@
         <v>70.59999999999999</v>
       </c>
       <c r="E4188" t="n">
-        <v>70.84999999999999</v>
+        <v>70.88</v>
       </c>
       <c r="F4188" t="n">
         <v>3662</v>
@@ -84201,7 +84201,7 @@
         <v>69.90000000000001</v>
       </c>
       <c r="E4189" t="n">
-        <v>69.92</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="F4189" t="n">
         <v>8190</v>
@@ -84238,13 +84238,33 @@
         <v>76.59999999999999</v>
       </c>
       <c r="D4191" t="n">
-        <v>76.15000000000001</v>
+        <v>75.53</v>
       </c>
       <c r="E4191" t="n">
-        <v>76.3</v>
+        <v>75.91</v>
       </c>
       <c r="F4191" t="n">
-        <v>299</v>
+        <v>7570</v>
+      </c>
+    </row>
+    <row r="4192">
+      <c r="A4192" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B4192" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="C4192" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="D4192" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="E4192" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="F4192" t="n">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4192"/>
+  <dimension ref="A1:F4193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84241,7 +84241,7 @@
         <v>75.53</v>
       </c>
       <c r="E4191" t="n">
-        <v>75.91</v>
+        <v>75.95</v>
       </c>
       <c r="F4191" t="n">
         <v>7570</v>
@@ -84255,16 +84255,36 @@
         <v>75.88</v>
       </c>
       <c r="C4192" t="n">
-        <v>76.03</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="D4192" t="n">
         <v>75.78</v>
       </c>
       <c r="E4192" t="n">
-        <v>75.98999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="F4192" t="n">
-        <v>71</v>
+        <v>4749</v>
+      </c>
+    </row>
+    <row r="4193">
+      <c r="A4193" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B4193" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="C4193" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="D4193" t="n">
+        <v>76</v>
+      </c>
+      <c r="E4193" t="n">
+        <v>76.37</v>
+      </c>
+      <c r="F4193" t="n">
+        <v>526</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4193"/>
+  <dimension ref="A1:F4194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84275,16 +84275,36 @@
         <v>76.2</v>
       </c>
       <c r="C4193" t="n">
-        <v>76.39</v>
+        <v>76.56</v>
       </c>
       <c r="D4193" t="n">
-        <v>76</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="E4193" t="n">
-        <v>76.37</v>
+        <v>76.42</v>
       </c>
       <c r="F4193" t="n">
-        <v>526</v>
+        <v>5112</v>
+      </c>
+    </row>
+    <row r="4194">
+      <c r="A4194" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4194" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="C4194" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="D4194" t="n">
+        <v>76.26000000000001</v>
+      </c>
+      <c r="E4194" t="n">
+        <v>76.34999999999999</v>
+      </c>
+      <c r="F4194" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4194"/>
+  <dimension ref="A1:F4195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84295,16 +84295,36 @@
         <v>76.26000000000001</v>
       </c>
       <c r="C4194" t="n">
-        <v>76.40000000000001</v>
+        <v>76.86</v>
       </c>
       <c r="D4194" t="n">
         <v>76.26000000000001</v>
       </c>
       <c r="E4194" t="n">
-        <v>76.34999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="F4194" t="n">
-        <v>30</v>
+        <v>5392</v>
+      </c>
+    </row>
+    <row r="4195">
+      <c r="A4195" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B4195" t="n">
+        <v>76.31999999999999</v>
+      </c>
+      <c r="C4195" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="D4195" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="E4195" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="F4195" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4195"/>
+  <dimension ref="A1:F4196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84315,16 +84315,36 @@
         <v>76.31999999999999</v>
       </c>
       <c r="C4195" t="n">
-        <v>76.5</v>
+        <v>77</v>
       </c>
       <c r="D4195" t="n">
         <v>76.25</v>
       </c>
       <c r="E4195" t="n">
-        <v>76.44</v>
+        <v>76.8</v>
       </c>
       <c r="F4195" t="n">
-        <v>76</v>
+        <v>5852</v>
+      </c>
+    </row>
+    <row r="4196">
+      <c r="A4196" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B4196" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="C4196" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="D4196" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="E4196" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="F4196" t="n">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4196"/>
+  <dimension ref="A1:F4197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84338,13 +84338,33 @@
         <v>76.98</v>
       </c>
       <c r="D4196" t="n">
-        <v>76.79000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="E4196" t="n">
-        <v>76.98</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="F4196" t="n">
-        <v>125</v>
+        <v>8447</v>
+      </c>
+    </row>
+    <row r="4197">
+      <c r="A4197" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4197" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="C4197" t="n">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="D4197" t="n">
+        <v>75.69</v>
+      </c>
+      <c r="E4197" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="F4197" t="n">
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4197"/>
+  <dimension ref="A1:F4198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84341,7 +84341,7 @@
         <v>75.8</v>
       </c>
       <c r="E4196" t="n">
-        <v>75.98999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F4196" t="n">
         <v>8447</v>
@@ -84355,16 +84355,36 @@
         <v>75.81</v>
       </c>
       <c r="C4197" t="n">
-        <v>76.01000000000001</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="D4197" t="n">
-        <v>75.69</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="E4197" t="n">
-        <v>75.90000000000001</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="F4197" t="n">
-        <v>425</v>
+        <v>4996</v>
+      </c>
+    </row>
+    <row r="4198">
+      <c r="A4198" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B4198" t="n">
+        <v>75.98999999999999</v>
+      </c>
+      <c r="C4198" t="n">
+        <v>76.09</v>
+      </c>
+      <c r="D4198" t="n">
+        <v>75.95999999999999</v>
+      </c>
+      <c r="E4198" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="F4198" t="n">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4198"/>
+  <dimension ref="A1:F4199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84375,16 +84375,36 @@
         <v>75.98999999999999</v>
       </c>
       <c r="C4198" t="n">
-        <v>76.09</v>
+        <v>76.19</v>
       </c>
       <c r="D4198" t="n">
-        <v>75.95999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="E4198" t="n">
-        <v>76.02</v>
+        <v>75.86</v>
       </c>
       <c r="F4198" t="n">
-        <v>133</v>
+        <v>4472</v>
+      </c>
+    </row>
+    <row r="4199">
+      <c r="A4199" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B4199" t="n">
+        <v>75.81999999999999</v>
+      </c>
+      <c r="C4199" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="D4199" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="E4199" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="F4199" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4199"/>
+  <dimension ref="A1:F4200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84398,13 +84398,33 @@
         <v>75.90000000000001</v>
       </c>
       <c r="D4199" t="n">
-        <v>75.81</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E4199" t="n">
-        <v>75.84999999999999</v>
+        <v>75.52</v>
       </c>
       <c r="F4199" t="n">
-        <v>57</v>
+        <v>14357</v>
+      </c>
+    </row>
+    <row r="4200">
+      <c r="A4200" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4200" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="C4200" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="D4200" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="E4200" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="F4200" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4200"/>
+  <dimension ref="A1:F4201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84418,13 +84418,33 @@
         <v>75.72</v>
       </c>
       <c r="D4200" t="n">
-        <v>75.44</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E4200" t="n">
-        <v>75.55</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="F4200" t="n">
-        <v>94</v>
+        <v>8452</v>
+      </c>
+    </row>
+    <row r="4201">
+      <c r="A4201" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B4201" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="C4201" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="D4201" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="E4201" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="F4201" t="n">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4201"/>
+  <dimension ref="A1:F4202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84435,16 +84435,36 @@
         <v>74.44</v>
       </c>
       <c r="C4201" t="n">
-        <v>74.5</v>
+        <v>74.69</v>
       </c>
       <c r="D4201" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="E4201" t="n">
-        <v>74.44</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="F4201" t="n">
-        <v>82</v>
+        <v>6020</v>
+      </c>
+    </row>
+    <row r="4202">
+      <c r="A4202" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4202" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="C4202" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="D4202" t="n">
+        <v>74.12</v>
+      </c>
+      <c r="E4202" t="n">
+        <v>74.18000000000001</v>
+      </c>
+      <c r="F4202" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4202"/>
+  <dimension ref="A1:F4203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84381,7 +84381,7 @@
         <v>75.7</v>
       </c>
       <c r="E4198" t="n">
-        <v>75.86</v>
+        <v>75.88</v>
       </c>
       <c r="F4198" t="n">
         <v>4472</v>
@@ -84421,7 +84421,7 @@
         <v>74.40000000000001</v>
       </c>
       <c r="E4200" t="n">
-        <v>74.43000000000001</v>
+        <v>74.44</v>
       </c>
       <c r="F4200" t="n">
         <v>8452</v>
@@ -84458,13 +84458,33 @@
         <v>74.34</v>
       </c>
       <c r="D4202" t="n">
-        <v>74.12</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E4202" t="n">
-        <v>74.18000000000001</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="F4202" t="n">
-        <v>74</v>
+        <v>14542</v>
+      </c>
+    </row>
+    <row r="4203">
+      <c r="A4203" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4203" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="C4203" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="D4203" t="n">
+        <v>72</v>
+      </c>
+      <c r="E4203" t="n">
+        <v>72.23</v>
+      </c>
+      <c r="F4203" t="n">
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4203"/>
+  <dimension ref="A1:F4204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84475,16 +84475,36 @@
         <v>72.06999999999999</v>
       </c>
       <c r="C4203" t="n">
-        <v>72.25</v>
+        <v>72.38</v>
       </c>
       <c r="D4203" t="n">
-        <v>72</v>
+        <v>71.58</v>
       </c>
       <c r="E4203" t="n">
-        <v>72.23</v>
+        <v>72.12</v>
       </c>
       <c r="F4203" t="n">
-        <v>258</v>
+        <v>11608</v>
+      </c>
+    </row>
+    <row r="4204">
+      <c r="A4204" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4204" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="C4204" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="D4204" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="E4204" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="F4204" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4204"/>
+  <dimension ref="A1:F4205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84495,16 +84495,36 @@
         <v>72.2</v>
       </c>
       <c r="C4204" t="n">
-        <v>72.3</v>
+        <v>72.39</v>
       </c>
       <c r="D4204" t="n">
-        <v>72.06</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E4204" t="n">
-        <v>72.15000000000001</v>
+        <v>71.67</v>
       </c>
       <c r="F4204" t="n">
-        <v>75</v>
+        <v>8153</v>
+      </c>
+    </row>
+    <row r="4205">
+      <c r="A4205" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B4205" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="C4205" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D4205" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E4205" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="F4205" t="n">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4205"/>
+  <dimension ref="A1:F4206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84518,13 +84518,33 @@
         <v>71.8</v>
       </c>
       <c r="D4205" t="n">
-        <v>71.5</v>
+        <v>70.33</v>
       </c>
       <c r="E4205" t="n">
-        <v>71.5</v>
+        <v>70.53</v>
       </c>
       <c r="F4205" t="n">
-        <v>187</v>
+        <v>13092</v>
+      </c>
+    </row>
+    <row r="4206">
+      <c r="A4206" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B4206" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="C4206" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="D4206" t="n">
+        <v>70.37</v>
+      </c>
+      <c r="E4206" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F4206" t="n">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4206"/>
+  <dimension ref="A1:F4207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84538,13 +84538,33 @@
         <v>70.65000000000001</v>
       </c>
       <c r="D4206" t="n">
-        <v>70.37</v>
+        <v>69.5</v>
       </c>
       <c r="E4206" t="n">
-        <v>70.5</v>
+        <v>69.81</v>
       </c>
       <c r="F4206" t="n">
-        <v>146</v>
+        <v>7324</v>
+      </c>
+    </row>
+    <row r="4207">
+      <c r="A4207" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B4207" t="n">
+        <v>69.73</v>
+      </c>
+      <c r="C4207" t="n">
+        <v>69.88</v>
+      </c>
+      <c r="D4207" t="n">
+        <v>69.73</v>
+      </c>
+      <c r="E4207" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="F4207" t="n">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4207"/>
+  <dimension ref="A1:F4208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84555,16 +84555,36 @@
         <v>69.73</v>
       </c>
       <c r="C4207" t="n">
-        <v>69.88</v>
+        <v>70.69</v>
       </c>
       <c r="D4207" t="n">
-        <v>69.73</v>
+        <v>69.66</v>
       </c>
       <c r="E4207" t="n">
-        <v>69.83</v>
+        <v>69.92</v>
       </c>
       <c r="F4207" t="n">
-        <v>122</v>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4208">
+      <c r="A4208" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B4208" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="C4208" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="D4208" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E4208" t="n">
+        <v>69.84</v>
+      </c>
+      <c r="F4208" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4208"/>
+  <dimension ref="A1:F4209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84575,16 +84575,36 @@
         <v>69.92</v>
       </c>
       <c r="C4208" t="n">
-        <v>69.95</v>
+        <v>70.3</v>
       </c>
       <c r="D4208" t="n">
-        <v>69.8</v>
+        <v>69.3</v>
       </c>
       <c r="E4208" t="n">
-        <v>69.84</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="F4208" t="n">
-        <v>48</v>
+        <v>9364</v>
+      </c>
+    </row>
+    <row r="4209">
+      <c r="A4209" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B4209" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="C4209" t="n">
+        <v>69.59</v>
+      </c>
+      <c r="D4209" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="E4209" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F4209" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4209"/>
+  <dimension ref="A1:F4210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84595,16 +84595,36 @@
         <v>69.52</v>
       </c>
       <c r="C4209" t="n">
-        <v>69.59</v>
+        <v>69.66</v>
       </c>
       <c r="D4209" t="n">
-        <v>69.47</v>
+        <v>68.03</v>
       </c>
       <c r="E4209" t="n">
-        <v>69.5</v>
+        <v>68.7</v>
       </c>
       <c r="F4209" t="n">
-        <v>76</v>
+        <v>12911</v>
+      </c>
+    </row>
+    <row r="4210">
+      <c r="A4210" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B4210" t="n">
+        <v>68.70999999999999</v>
+      </c>
+      <c r="C4210" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="D4210" t="n">
+        <v>68.66</v>
+      </c>
+      <c r="E4210" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="F4210" t="n">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -84601,7 +84601,7 @@
         <v>68.03</v>
       </c>
       <c r="E4209" t="n">
-        <v>68.7</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="F4209" t="n">
         <v>12911</v>
@@ -84621,7 +84621,7 @@
         <v>68.66</v>
       </c>
       <c r="E4210" t="n">
-        <v>68.69</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="F4210" t="n">
         <v>146</v>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4210"/>
+  <dimension ref="A1:F4211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84615,16 +84615,36 @@
         <v>68.70999999999999</v>
       </c>
       <c r="C4210" t="n">
-        <v>68.89</v>
+        <v>69.58</v>
       </c>
       <c r="D4210" t="n">
-        <v>68.66</v>
+        <v>68.5</v>
       </c>
       <c r="E4210" t="n">
-        <v>68.70999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="F4210" t="n">
-        <v>146</v>
+        <v>8248</v>
+      </c>
+    </row>
+    <row r="4211">
+      <c r="A4211" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4211" t="n">
+        <v>68.94</v>
+      </c>
+      <c r="C4211" t="n">
+        <v>69</v>
+      </c>
+      <c r="D4211" t="n">
+        <v>68.79000000000001</v>
+      </c>
+      <c r="E4211" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="F4211" t="n">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4211"/>
+  <dimension ref="A1:F4212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84638,13 +84638,33 @@
         <v>69</v>
       </c>
       <c r="D4211" t="n">
-        <v>68.79000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="E4211" t="n">
-        <v>68.95</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F4211" t="n">
-        <v>188</v>
+        <v>6578</v>
+      </c>
+    </row>
+    <row r="4212">
+      <c r="A4212" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4212" t="n">
+        <v>67.45</v>
+      </c>
+      <c r="C4212" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="D4212" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="E4212" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="F4212" t="n">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4212"/>
+  <dimension ref="A1:F4213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84621,7 +84621,7 @@
         <v>68.5</v>
       </c>
       <c r="E4210" t="n">
-        <v>68.95</v>
+        <v>68.97</v>
       </c>
       <c r="F4210" t="n">
         <v>8248</v>
@@ -84655,16 +84655,36 @@
         <v>67.45</v>
       </c>
       <c r="C4212" t="n">
-        <v>67.48</v>
+        <v>67.55</v>
       </c>
       <c r="D4212" t="n">
-        <v>67.36</v>
+        <v>66.75</v>
       </c>
       <c r="E4212" t="n">
-        <v>67.36</v>
+        <v>67.09</v>
       </c>
       <c r="F4212" t="n">
-        <v>61</v>
+        <v>8327</v>
+      </c>
+    </row>
+    <row r="4213">
+      <c r="A4213" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4213" t="n">
+        <v>67</v>
+      </c>
+      <c r="C4213" t="n">
+        <v>67.20999999999999</v>
+      </c>
+      <c r="D4213" t="n">
+        <v>67</v>
+      </c>
+      <c r="E4213" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F4213" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4213"/>
+  <dimension ref="A1:F4214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84621,7 +84621,7 @@
         <v>68.5</v>
       </c>
       <c r="E4210" t="n">
-        <v>68.97</v>
+        <v>68.95</v>
       </c>
       <c r="F4210" t="n">
         <v>8248</v>
@@ -84678,13 +84678,33 @@
         <v>67.20999999999999</v>
       </c>
       <c r="D4213" t="n">
-        <v>67</v>
+        <v>66.27</v>
       </c>
       <c r="E4213" t="n">
-        <v>67.09999999999999</v>
+        <v>66.63</v>
       </c>
       <c r="F4213" t="n">
-        <v>52</v>
+        <v>9473</v>
+      </c>
+    </row>
+    <row r="4214">
+      <c r="A4214" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4214" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="C4214" t="n">
+        <v>66.77</v>
+      </c>
+      <c r="D4214" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E4214" t="n">
+        <v>66.77</v>
+      </c>
+      <c r="F4214" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4214"/>
+  <dimension ref="A1:F4215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84621,7 +84621,7 @@
         <v>68.5</v>
       </c>
       <c r="E4210" t="n">
-        <v>68.95</v>
+        <v>68.97</v>
       </c>
       <c r="F4210" t="n">
         <v>8248</v>
@@ -84641,7 +84641,7 @@
         <v>67.3</v>
       </c>
       <c r="E4211" t="n">
-        <v>67.40000000000001</v>
+        <v>67.39</v>
       </c>
       <c r="F4211" t="n">
         <v>6578</v>
@@ -84695,16 +84695,36 @@
         <v>66.59999999999999</v>
       </c>
       <c r="C4214" t="n">
-        <v>66.77</v>
+        <v>66.98</v>
       </c>
       <c r="D4214" t="n">
-        <v>66.59999999999999</v>
+        <v>65.87</v>
       </c>
       <c r="E4214" t="n">
-        <v>66.77</v>
+        <v>65.94</v>
       </c>
       <c r="F4214" t="n">
-        <v>51</v>
+        <v>4592</v>
+      </c>
+    </row>
+    <row r="4215">
+      <c r="A4215" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4215" t="n">
+        <v>65.88</v>
+      </c>
+      <c r="C4215" t="n">
+        <v>65.94</v>
+      </c>
+      <c r="D4215" t="n">
+        <v>65.66</v>
+      </c>
+      <c r="E4215" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="F4215" t="n">
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4215"/>
+  <dimension ref="A1:F4216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84715,16 +84715,36 @@
         <v>65.88</v>
       </c>
       <c r="C4215" t="n">
-        <v>65.94</v>
+        <v>66.22</v>
       </c>
       <c r="D4215" t="n">
-        <v>65.66</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E4215" t="n">
-        <v>65.8</v>
+        <v>65.91</v>
       </c>
       <c r="F4215" t="n">
-        <v>401</v>
+        <v>8955</v>
+      </c>
+    </row>
+    <row r="4216">
+      <c r="A4216" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4216" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="C4216" t="n">
+        <v>65.91</v>
+      </c>
+      <c r="D4216" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="E4216" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="F4216" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4216"/>
+  <dimension ref="A1:F4217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84738,13 +84738,33 @@
         <v>65.91</v>
       </c>
       <c r="D4216" t="n">
-        <v>65.81999999999999</v>
+        <v>65.37</v>
       </c>
       <c r="E4216" t="n">
-        <v>65.87</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="F4216" t="n">
-        <v>37</v>
+        <v>6625</v>
+      </c>
+    </row>
+    <row r="4217">
+      <c r="A4217" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4217" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="C4217" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="D4217" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="E4217" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="F4217" t="n">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4217"/>
+  <dimension ref="A1:F4218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84755,16 +84755,36 @@
         <v>65.59999999999999</v>
       </c>
       <c r="C4217" t="n">
-        <v>65.67</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="D4217" t="n">
-        <v>65.52</v>
+        <v>65.42</v>
       </c>
       <c r="E4217" t="n">
-        <v>65.52</v>
+        <v>65.55</v>
       </c>
       <c r="F4217" t="n">
-        <v>72</v>
+        <v>6538</v>
+      </c>
+    </row>
+    <row r="4218">
+      <c r="A4218" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4218" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="C4218" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="D4218" t="n">
+        <v>65.41</v>
+      </c>
+      <c r="E4218" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="F4218" t="n">
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4218"/>
+  <dimension ref="A1:F4219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84778,13 +84778,33 @@
         <v>65.64</v>
       </c>
       <c r="D4218" t="n">
-        <v>65.41</v>
+        <v>65.03</v>
       </c>
       <c r="E4218" t="n">
-        <v>65.45</v>
+        <v>65.53</v>
       </c>
       <c r="F4218" t="n">
-        <v>217</v>
+        <v>6356</v>
+      </c>
+    </row>
+    <row r="4219">
+      <c r="A4219" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4219" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="C4219" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="D4219" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="E4219" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="F4219" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4219"/>
+  <dimension ref="A1:F4220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84781,7 +84781,7 @@
         <v>65.03</v>
       </c>
       <c r="E4218" t="n">
-        <v>65.53</v>
+        <v>65.36</v>
       </c>
       <c r="F4218" t="n">
         <v>6356</v>
@@ -84795,16 +84795,36 @@
         <v>65.62</v>
       </c>
       <c r="C4219" t="n">
-        <v>65.62</v>
+        <v>68.63</v>
       </c>
       <c r="D4219" t="n">
         <v>65.28</v>
       </c>
       <c r="E4219" t="n">
-        <v>65.31</v>
+        <v>66.89</v>
       </c>
       <c r="F4219" t="n">
-        <v>32</v>
+        <v>10633</v>
+      </c>
+    </row>
+    <row r="4220">
+      <c r="A4220" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4220" t="n">
+        <v>66.98</v>
+      </c>
+      <c r="C4220" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="D4220" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E4220" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="F4220" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4220"/>
+  <dimension ref="A1:F4221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84815,16 +84815,36 @@
         <v>66.98</v>
       </c>
       <c r="C4220" t="n">
-        <v>66.98999999999999</v>
+        <v>67</v>
       </c>
       <c r="D4220" t="n">
-        <v>66.8</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="E4220" t="n">
-        <v>66.87</v>
+        <v>66.39</v>
       </c>
       <c r="F4220" t="n">
-        <v>86</v>
+        <v>6860</v>
+      </c>
+    </row>
+    <row r="4221">
+      <c r="A4221" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4221" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="C4221" t="n">
+        <v>66.72</v>
+      </c>
+      <c r="D4221" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="E4221" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="F4221" t="n">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4221"/>
+  <dimension ref="A1:F4222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84835,16 +84835,36 @@
         <v>66.34999999999999</v>
       </c>
       <c r="C4221" t="n">
-        <v>66.72</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="D4221" t="n">
         <v>66.23999999999999</v>
       </c>
       <c r="E4221" t="n">
-        <v>66.59999999999999</v>
+        <v>66.73</v>
       </c>
       <c r="F4221" t="n">
-        <v>135</v>
+        <v>5129</v>
+      </c>
+    </row>
+    <row r="4222">
+      <c r="A4222" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4222" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="C4222" t="n">
+        <v>66.98</v>
+      </c>
+      <c r="D4222" t="n">
+        <v>66.72</v>
+      </c>
+      <c r="E4222" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F4222" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4222"/>
+  <dimension ref="A1:F4223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84855,16 +84855,36 @@
         <v>66.73999999999999</v>
       </c>
       <c r="C4222" t="n">
-        <v>66.98</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="D4222" t="n">
-        <v>66.72</v>
+        <v>66.13</v>
       </c>
       <c r="E4222" t="n">
-        <v>66.8</v>
+        <v>67.28</v>
       </c>
       <c r="F4222" t="n">
-        <v>38</v>
+        <v>4422</v>
+      </c>
+    </row>
+    <row r="4223">
+      <c r="A4223" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B4223" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="C4223" t="n">
+        <v>67.43000000000001</v>
+      </c>
+      <c r="D4223" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="E4223" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="F4223" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4223"/>
+  <dimension ref="A1:F4224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84875,16 +84875,36 @@
         <v>67.23</v>
       </c>
       <c r="C4223" t="n">
-        <v>67.43000000000001</v>
+        <v>68</v>
       </c>
       <c r="D4223" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="E4223" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="F4223" t="n">
+        <v>5015</v>
+      </c>
+    </row>
+    <row r="4224">
+      <c r="A4224" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B4224" t="n">
+        <v>67.27</v>
+      </c>
+      <c r="C4224" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="D4224" t="n">
         <v>67.23</v>
       </c>
-      <c r="E4223" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="F4223" t="n">
-        <v>66</v>
+      <c r="E4224" t="n">
+        <v>67.34999999999999</v>
+      </c>
+      <c r="F4224" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
